--- a/data/trans_camb/P8_1_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P8_1_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,91</t>
+          <t>-1,55; 1,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,34</t>
+          <t>-2,63; 0,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,81</t>
+          <t>-1,43; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,26</t>
+          <t>-1,21; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,89</t>
+          <t>-1,68; 2,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,42</t>
+          <t>-3,4; 0,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,01</t>
+          <t>-0,88; 2,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,08</t>
+          <t>-1,53; 0,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,45</t>
+          <t>-1,77; 1,83</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,91; 269,29</t>
+          <t>-64,88; 241,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,41</t>
+          <t>-100,0; 76,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 396,99</t>
+          <t>-78,37; 444,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,56; 230,88</t>
+          <t>-40,84; 211,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 226,77</t>
+          <t>-51,79; 208,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,84; 75,12</t>
+          <t>-98,56; 73,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 139,59</t>
+          <t>-32,44; 138,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,07; 80,44</t>
+          <t>-60,21; 72,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,9; 111,58</t>
+          <t>-75,16; 157,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,55</t>
+          <t>-1,43; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,41</t>
+          <t>-1,61; 2,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,99</t>
+          <t>-0,29; 5,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,17</t>
+          <t>-2,7; 2,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,9</t>
+          <t>-2,97; 2,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -1,69</t>
+          <t>-6,34; -1,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,71</t>
+          <t>-1,39; 1,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,76</t>
+          <t>-1,52; 1,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,13</t>
+          <t>-2,56; 1,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 120,23</t>
+          <t>-36,87; 110,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 108,27</t>
+          <t>-43,52; 94,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 250,79</t>
+          <t>-10,83; 270,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 56,09</t>
+          <t>-47,11; 58,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 51,99</t>
+          <t>-46,88; 59,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,06; -42,29</t>
+          <t>-92,74; -44,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 57,22</t>
+          <t>-30,14; 54,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 53,49</t>
+          <t>-33,78; 46,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 34,9</t>
+          <t>-57,72; 35,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,18</t>
+          <t>-0,41; 4,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,39</t>
+          <t>-1,23; 3,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,94</t>
+          <t>-0,91; 4,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,77</t>
+          <t>0,02; 6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,46</t>
+          <t>-3,42; 2,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,97</t>
+          <t>-4,11; 1,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,94</t>
+          <t>0,56; 4,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,26</t>
+          <t>-1,72; 2,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,26</t>
+          <t>-1,62; 2,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 137,32</t>
+          <t>-9,41; 146,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 117,59</t>
+          <t>-24,37; 117,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 126,54</t>
+          <t>-20,25; 137,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 104,93</t>
+          <t>0,07; 94,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 38,81</t>
+          <t>-36,36; 35,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 29,21</t>
+          <t>-43,37; 25,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,84; 94,12</t>
+          <t>7,73; 90,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 46,29</t>
+          <t>-24,45; 43,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 43,3</t>
+          <t>-22,08; 43,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 7,21</t>
+          <t>0,09; 7,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,79</t>
+          <t>1,12; 8,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 66,12</t>
+          <t>2,8; 64,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 5,85</t>
+          <t>-2,8; 5,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,7</t>
+          <t>-3,95; 4,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 2,12</t>
+          <t>-5,79; 2,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 5,29</t>
+          <t>-0,48; 5,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,06</t>
+          <t>-0,56; 4,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 44,66</t>
+          <t>0,53; 40,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 124,85</t>
+          <t>-0,41; 123,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,2; 133,23</t>
+          <t>9,15; 148,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,35; 1196,66</t>
+          <t>36,17; 1057,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 44,83</t>
+          <t>-16,31; 46,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 36,78</t>
+          <t>-22,77; 37,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 16,91</t>
+          <t>-32,63; 20,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 52,89</t>
+          <t>-3,89; 52,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 52,84</t>
+          <t>-5,09; 50,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 429,2</t>
+          <t>4,0; 424,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,62</t>
+          <t>-6,86; 4,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,09</t>
+          <t>-7,38; 4,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,6</t>
+          <t>-5,75; 4,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 16,52</t>
+          <t>3,32; 15,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 10,18</t>
+          <t>-2,11; 10,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 2,02</t>
+          <t>-8,6; 2,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,13</t>
+          <t>-0,27; 8,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 5,13</t>
+          <t>-2,89; 5,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 1,66</t>
+          <t>-5,11; 2,34</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 25,66</t>
+          <t>-29,09; 28,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 23,43</t>
+          <t>-31,31; 24,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 26,06</t>
+          <t>-24,68; 25,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,07; 68,45</t>
+          <t>10,14; 65,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 40,74</t>
+          <t>-6,86; 42,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 8,53</t>
+          <t>-27,38; 9,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,45; 41,71</t>
+          <t>-1,03; 38,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 23,03</t>
+          <t>-11,05; 26,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 7,6</t>
+          <t>-19,14; 10,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,41; 15,28</t>
+          <t>-0,04; 15,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 10,55</t>
+          <t>-2,94; 11,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,66</t>
+          <t>-10,25; 1,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 8,86</t>
+          <t>-6,04; 9,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 1,38</t>
+          <t>-13,99; 0,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-45,54; -12,68</t>
+          <t>-44,15; -12,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,57</t>
+          <t>-1,98; 9,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 2,92</t>
+          <t>-6,9; 3,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-29,42; -8,91</t>
+          <t>-29,31; -8,18</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,86; 66,83</t>
+          <t>-0,04; 68,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 43,63</t>
+          <t>-9,62; 48,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 7,52</t>
+          <t>-33,28; 6,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 18,17</t>
+          <t>-10,72; 18,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 2,78</t>
+          <t>-24,46; 1,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,02; -24,37</t>
+          <t>-78,62; -24,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 24,9</t>
+          <t>-4,53; 23,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 7,66</t>
+          <t>-16,28; 7,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-67,31; -21,99</t>
+          <t>-68,78; -20,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,5; 23,14</t>
+          <t>3,93; 22,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 11,61</t>
+          <t>-6,27; 11,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 4,34</t>
+          <t>-11,98; 4,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 11,24</t>
+          <t>-1,6; 11,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 1,23</t>
+          <t>-13,33; 1,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 4,53</t>
+          <t>-7,51; 4,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,11</t>
+          <t>3,6; 14,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 2,76</t>
+          <t>-8,2; 2,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 2,47</t>
+          <t>-7,82; 2,44</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,55; 48,38</t>
+          <t>6,23; 47,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 24,52</t>
+          <t>-10,73; 24,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 9,13</t>
+          <t>-20,82; 10,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 15,71</t>
+          <t>-1,87; 16,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 1,59</t>
+          <t>-17,0; 1,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 6,47</t>
+          <t>-9,36; 5,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,36; 22,09</t>
+          <t>4,9; 22,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 4,23</t>
+          <t>-11,69; 4,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,95</t>
+          <t>-10,79; 3,94</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,17</t>
+          <t>1,83; 5,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,21</t>
+          <t>1,14; 4,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,99; 27,54</t>
+          <t>3,12; 27,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,93</t>
+          <t>1,86; 5,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,13</t>
+          <t>-0,6; 3,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,23</t>
+          <t>-5,18; 1,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,09</t>
+          <t>2,5; 5,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,35</t>
+          <t>0,56; 3,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,66; 14,55</t>
+          <t>0,72; 13,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>15,04; 49,25</t>
+          <t>15,63; 50,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8,69; 40,97</t>
+          <t>9,72; 40,77</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25,68; 257,17</t>
+          <t>27,24; 254,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,08; 29,41</t>
+          <t>8,41; 28,86</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 15,36</t>
+          <t>-2,68; 16,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 5,78</t>
+          <t>-23,32; 5,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,25; 32,01</t>
+          <t>14,81; 31,62</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>3,56; 21,05</t>
+          <t>3,29; 20,84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,72; 86,65</t>
+          <t>4,42; 82,99</t>
         </is>
       </c>
     </row>
